--- a/examples/dlux/01_prices_dlux.xlsx
+++ b/examples/dlux/01_prices_dlux.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Полировка кузова седан</t>
+          <t>Мойка двигателя седан</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Химчистка салона седан</t>
+          <t>Полировка кузова седан</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -531,26 +531,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ДЖИП</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Полировка фар седан</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Мойка кузова джип</t>
+          <t>Химчистка салона полная седан</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -559,16 +567,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Мойка кузова джип при сильном загрязнении</t>
+          <t>Химчистка салона частичная седан</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -577,80 +585,80 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Полировка кузова джип</t>
+          <t>Шиномонтаж 4 колеса седан</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>усл. ед.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Химчистка салона джип</t>
+          <t>Балансировка 4 колеса седан</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>усл. ед.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>МИКРОАВТОБУС</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Антикоррозийная обработка днища седан</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>9</v>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Мойка кузова микроавтобус</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>усл. ед.</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1800</v>
-      </c>
+          <t>ДЖИП</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Полировка микроавтобус</t>
+          <t>Мойка кузова джип</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -659,7 +667,359 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Мойка кузова джип при сильном загрязнении</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Мойка двигателя джип</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Полировка кузова джип</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Полировка фар джип</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Химчистка салона полная джип</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Химчистка салона частичная джип</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Шиномонтаж 4 колеса джип</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Балансировка 4 колеса джип</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Антикоррозийная обработка днища джип</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>МИКРОАВТОБУС</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Мойка кузова микроавтобус</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Мойка кузова микроавтобус при сильном загрязнении</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Мойка двигателя микроавтобус</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Полировка кузова микроавтобус</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>2800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Полировка фар микроавтобус</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Химчистка салона полная микроавтобус</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Химчистка салона частичная микроавтобус</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Шиномонтаж 4 колеса микроавтобус</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Балансировка 4 колеса микроавтобус</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Антикоррозийная обработка днища микроавтобус</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7200</v>
       </c>
     </row>
   </sheetData>
